--- a/data/transactions.xlsx
+++ b/data/transactions.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transactions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -79,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -87,6 +88,7 @@
     <xf numFmtId="164" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -525,99 +527,289 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Monthly Budget</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Groceries</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Eating Out</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>120</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Subscriptions</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>950</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Shopping</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Entertainment</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Example row - edit or delete freely</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>How to use this file</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr"/>
+      <c r="A2" s="7" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>1. Add one row per transaction on the 'Transactions' tab, directly under the existing rows.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>2. Keep the highlighted example row (row 2) as a formatting reference, or delete it once you have your own data - it's not required.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>3. Columns:</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">   - Date: the transaction date (any recognisable date format).</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">   - Description: merchant / payee / memo text.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">   - Category: e.g. Groceries, Rent, Transport, Eating Out, Subscriptions, Utilities, Travel, Salary.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">   - Amount: enter spending as a POSITIVE number and income/refunds as a NEGATIVE number.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">     (If your bank statements do the opposite, just tick the 'negative = spending' box in the dashboard sidebar.)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">   - Account: which bank account or card the transaction is on.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>4. Save the file, then click 'Reload data' in the dashboard sidebar (or just refresh the browser tab).</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr"/>
+      <c r="A13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Do not rename the 'Transactions' sheet or its column headers - the dashboard reads them by name.</t>
+          <t>Setting a budget</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>5. On the 'Budget' tab, enter one row per category with the amount you want to spend per month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   A few starter rows are included - edit the amounts, and add or delete rows to match your own categories.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>6. Use the 'Notes' column for anything worth remembering, e.g. 'going up after rent renewal in March'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>7. Open the dashboard's 'Budget vs Actual' page (in the page menu) to see how you're tracking each month,</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   which categories are over, and exactly which transactions are driving it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>8. You can also edit the budget from inside that page and click 'Save budget to Excel' - it writes back</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   to this same file, so both routes always stay in sync.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Do not rename the 'Transactions' or 'Budget' sheets or their column headers - the dashboard reads them by name.</t>
         </is>
       </c>
     </row>
